--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,206 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133851039</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91940</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>631732</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092928</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133850799</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92643</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skogen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>631732</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92643</v>
+        <v>92649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92649</v>
+        <v>92651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92651</v>
+        <v>92172</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92172</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>133851039</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>133850799</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80675735</v>
+        <v>80675736</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mesjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631643.9639974314</v>
+        <v>631763</v>
       </c>
       <c r="R2" t="n">
-        <v>7092913.156166006</v>
+        <v>7092757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +743,9 @@
           <t>2019-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +781,7 @@
         <v>80675737</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631913.8130125989</v>
+        <v>631914</v>
       </c>
       <c r="R3" t="n">
-        <v>7092629.987981894</v>
+        <v>7092630</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +846,9 @@
           <t>2019-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,50 +881,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80675736</v>
+        <v>133850799</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mesjöberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631762.9635097674</v>
+        <v>631732</v>
       </c>
       <c r="R4" t="n">
-        <v>7092757.032079992</v>
+        <v>7092928</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,22 +946,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-08-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,34 +965,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133851039</v>
+        <v>80675735</v>
       </c>
       <c r="B5" t="n">
-        <v>91987</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,30 +994,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Mesjöberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631732</v>
+        <v>631644</v>
       </c>
       <c r="R5" t="n">
-        <v>7092928</v>
+        <v>7092913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-35</t>
+          <t>2019-08-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,123 +1065,27 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>133850799</v>
-      </c>
-      <c r="B6" t="n">
-        <v>92192</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Skogen, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>631732</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7092928</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Åsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-31</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22110-2024 artfynd.xlsx
+++ b/artfynd/A 22110-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675736</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675737</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80675735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>